--- a/docs/reviews/2026-10-22-t02-t03-tarot-copy-workbook.xlsx
+++ b/docs/reviews/2026-10-22-t02-t03-tarot-copy-workbook.xlsx
@@ -871,8 +871,16 @@
 self_care (Bản thân): Trùng Năng lượng (nhận lời khi đang cạn sức); dùng dòng Năng lượng.</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="n"/>
-      <c r="R2" s="6" t="n"/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Neutral fallback, natural; A reuses the typed-then-deleted motif</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="49" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -947,8 +955,16 @@
       </c>
       <c r="O3" s="5" t="inlineStr"/>
       <c r="P3" s="5" t="inlineStr"/>
-      <c r="Q3" s="6" t="n"/>
-      <c r="R3" s="6" t="n"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. A "Bạn mới quen… hỏi bạn" is ambiguous (friend vs you) and "nằm đó… đó" clunky</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="49" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -1023,8 +1039,16 @@
       </c>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="6" t="n"/>
-      <c r="R4" s="6" t="n"/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. A matches "sếp vừa giao" and shows the full week; B is a meeting nomination</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -1099,8 +1123,16 @@
       </c>
       <c r="O5" s="5" t="inlineStr"/>
       <c r="P5" s="5" t="inlineStr"/>
-      <c r="Q5" s="6" t="n"/>
-      <c r="R5" s="6" t="n"/>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Energy row: B shows the tiredness; A only says just got home (unsure, A fits the example dinner better)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -1175,8 +1207,16 @@
       </c>
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="6" t="n"/>
-      <c r="R6" s="6" t="n"/>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete conflict (three evenings booked), neutral</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -1251,8 +1291,16 @@
       </c>
       <c r="O7" s="5" t="inlineStr"/>
       <c r="P7" s="5" t="inlineStr"/>
-      <c r="Q7" s="6" t="n"/>
-      <c r="R7" s="6" t="n"/>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. More concrete (seen since last night); A is the generic hesitation motif</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="49" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -1327,8 +1375,16 @@
       </c>
       <c r="O8" s="5" t="inlineStr"/>
       <c r="P8" s="5" t="inlineStr"/>
-      <c r="Q8" s="6" t="n"/>
-      <c r="R8" s="6" t="n"/>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. A is exactly the shift-swap question; B is a different request</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="49" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -1403,8 +1459,16 @@
       </c>
       <c r="O9" s="5" t="inlineStr"/>
       <c r="P9" s="5" t="inlineStr"/>
-      <c r="Q9" s="6" t="n"/>
-      <c r="R9" s="6" t="n"/>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Late-night friend request matches the question; B is a group task</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="49" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -1479,8 +1543,16 @@
       </c>
       <c r="O10" s="5" t="inlineStr"/>
       <c r="P10" s="5" t="inlineStr"/>
-      <c r="Q10" s="6" t="n"/>
-      <c r="R10" s="6" t="n"/>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Exhaustion plus tonight invite, matches question</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
@@ -1555,8 +1627,16 @@
       </c>
       <c r="O11" s="5" t="inlineStr"/>
       <c r="P11" s="5" t="inlineStr"/>
-      <c r="Q11" s="6" t="n"/>
-      <c r="R11" s="6" t="n"/>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete request ("gấp") into saved evening; B also fine</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="49" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -1635,8 +1715,16 @@
           <t>energy (Năng lượng): Nói ra khi đang mệt thường khớp nhãn nhờ giúp / đặt ranh giới; dùng dòng Một chuyện làm dự phòng.</t>
         </is>
       </c>
-      <c r="Q12" s="6" t="n"/>
-      <c r="R12" s="6" t="n"/>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Teasing scene matches question exactly, observable</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="49" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
@@ -1711,8 +1799,16 @@
       </c>
       <c r="O13" s="5" t="inlineStr"/>
       <c r="P13" s="5" t="inlineStr"/>
-      <c r="Q13" s="6" t="n"/>
-      <c r="R13" s="6" t="n"/>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. B shows not voicing the need ("sao cũng được"); A reads as disengagement</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="49" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
@@ -1787,8 +1883,16 @@
       </c>
       <c r="O14" s="5" t="inlineStr"/>
       <c r="P14" s="5" t="inlineStr"/>
-      <c r="Q14" s="6" t="n"/>
-      <c r="R14" s="6" t="n"/>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Nodding along to a deadline = unspoken objection</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="49" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -1863,8 +1967,16 @@
       </c>
       <c r="O15" s="5" t="inlineStr"/>
       <c r="P15" s="5" t="inlineStr"/>
-      <c r="Q15" s="6" t="n"/>
-      <c r="R15" s="6" t="n"/>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Short, vivid (mic on then off)</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -1939,8 +2051,16 @@
       </c>
       <c r="O16" s="5" t="inlineStr"/>
       <c r="P16" s="5" t="inlineStr"/>
-      <c r="Q16" s="6" t="n"/>
-      <c r="R16" s="6" t="n"/>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Concrete unspoken need; A "xoa thái dương" hints at a headache</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="94" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
@@ -2020,8 +2140,16 @@
 self_care (Bản thân): Nhắn lại không phải chuyện chăm mình; câu loại này rơi về Giao tiếp.</t>
         </is>
       </c>
-      <c r="Q17" s="6" t="n"/>
-      <c r="R17" s="6" t="n"/>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Matches "vừa hỏi thăm"; B is a year-old chat</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="49" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
@@ -2096,8 +2224,16 @@
       </c>
       <c r="O18" s="5" t="inlineStr"/>
       <c r="P18" s="5" t="inlineStr"/>
-      <c r="Q18" s="6" t="n"/>
-      <c r="R18" s="6" t="n"/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Neutral and observable; B repeats typed-deleted motif</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
@@ -2172,8 +2308,16 @@
       </c>
       <c r="O19" s="5" t="inlineStr"/>
       <c r="P19" s="5" t="inlineStr"/>
-      <c r="Q19" s="6" t="n"/>
-      <c r="R19" s="6" t="n"/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Exactly the evening client message; B is a colleague on a bus</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="49" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
@@ -2248,8 +2392,16 @@
       </c>
       <c r="O20" s="5" t="inlineStr"/>
       <c r="P20" s="5" t="inlineStr"/>
-      <c r="Q20" s="6" t="n"/>
-      <c r="R20" s="6" t="n"/>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Shows the misunderstanding from the message itself; B does not</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="64" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
@@ -2329,8 +2481,16 @@
 self_care (Bản thân): Hỏi lại không gắn với chăm mình; câu loại này rơi về Giao tiếp.</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="n"/>
-      <c r="R21" s="6" t="n"/>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Three people, three times, nobody confirmed: exact need to ask</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="34" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
@@ -2405,8 +2565,16 @@
       </c>
       <c r="O22" s="5" t="inlineStr"/>
       <c r="P22" s="5" t="inlineStr"/>
-      <c r="Q22" s="6" t="n"/>
-      <c r="R22" s="6" t="n"/>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. A repeats "chuyện" three times; B concrete</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
@@ -2481,8 +2649,16 @@
       </c>
       <c r="O23" s="5" t="inlineStr"/>
       <c r="P23" s="5" t="inlineStr"/>
-      <c r="Q23" s="6" t="n"/>
-      <c r="R23" s="6" t="n"/>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Two-minute hallway brief, three-word note: vivid and natural</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="49" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
@@ -2557,8 +2733,16 @@
       </c>
       <c r="O24" s="5" t="inlineStr"/>
       <c r="P24" s="5" t="inlineStr"/>
-      <c r="Q24" s="6" t="n"/>
-      <c r="R24" s="6" t="n"/>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. "ừ, tùy bạn" is exactly the unclear message</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="49" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
@@ -2637,8 +2821,16 @@
           <t>self_care (Bản thân): Chờ thêm trong chuyện chăm mình thường là nghỉ / dừng; dùng các nhãn đó.</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="n"/>
-      <c r="R25" s="6" t="n"/>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. B shows there is time and missing info; fits waiting</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="34" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
@@ -2713,8 +2905,16 @@
       </c>
       <c r="O26" s="5" t="inlineStr"/>
       <c r="P26" s="5" t="inlineStr"/>
-      <c r="Q26" s="6" t="n"/>
-      <c r="R26" s="6" t="n"/>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Last message is yours: matches "đợi nhắn trước"</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="49" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
@@ -2789,8 +2989,16 @@
       </c>
       <c r="O27" s="5" t="inlineStr"/>
       <c r="P27" s="5" t="inlineStr"/>
-      <c r="Q27" s="6" t="n"/>
-      <c r="R27" s="6" t="n"/>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. A says email shows "đã gửi" status (email does not show read state); B accurate</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="34" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
@@ -2865,8 +3073,16 @@
       </c>
       <c r="O28" s="5" t="inlineStr"/>
       <c r="P28" s="5" t="inlineStr"/>
-      <c r="Q28" s="6" t="n"/>
-      <c r="R28" s="6" t="n"/>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Hot-faced long reply with exclamation marks; B has trembling hands</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="34" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
@@ -2941,8 +3157,16 @@
       </c>
       <c r="O29" s="5" t="inlineStr"/>
       <c r="P29" s="5" t="inlineStr"/>
-      <c r="Q29" s="6" t="n"/>
-      <c r="R29" s="6" t="n"/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Late night, tired, two options: matches</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="49" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
@@ -3021,8 +3245,16 @@
           <t>communication (Giao tiếp): Bắt đầu một cuộc nói chuyện khớp nhãn nói ra / hẹn gặp (signal dài hơn thắng).</t>
         </is>
       </c>
-      <c r="Q30" s="6" t="n"/>
-      <c r="R30" s="6" t="n"/>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Unopened paint box: concrete, warm</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="49" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
@@ -3097,8 +3329,16 @@
       </c>
       <c r="O31" s="5" t="inlineStr"/>
       <c r="P31" s="5" t="inlineStr"/>
-      <c r="Q31" s="6" t="n"/>
-      <c r="R31" s="6" t="n"/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Shorter, warm; B also good</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="49" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
@@ -3173,8 +3413,16 @@
       </c>
       <c r="O32" s="5" t="inlineStr"/>
       <c r="P32" s="5" t="inlineStr"/>
-      <c r="Q32" s="6" t="n"/>
-      <c r="R32" s="6" t="n"/>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Renamed more than edited: concrete, light humour</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="34" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
@@ -3249,8 +3497,16 @@
       </c>
       <c r="O33" s="5" t="inlineStr"/>
       <c r="P33" s="5" t="inlineStr"/>
-      <c r="Q33" s="6" t="n"/>
-      <c r="R33" s="6" t="n"/>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Dusty shoes at the door: observable</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
@@ -3325,8 +3581,16 @@
       </c>
       <c r="O34" s="5" t="inlineStr"/>
       <c r="P34" s="5" t="inlineStr"/>
-      <c r="Q34" s="6" t="n"/>
-      <c r="R34" s="6" t="n"/>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Shorter, matches morning time</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="34" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
@@ -3401,8 +3665,16 @@
       </c>
       <c r="O35" s="5" t="inlineStr"/>
       <c r="P35" s="5" t="inlineStr"/>
-      <c r="Q35" s="6" t="n"/>
-      <c r="R35" s="6" t="n"/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete signs of the class not working</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="49" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
@@ -3477,8 +3749,16 @@
       </c>
       <c r="O36" s="5" t="inlineStr"/>
       <c r="P36" s="5" t="inlineStr"/>
-      <c r="Q36" s="6" t="n"/>
-      <c r="R36" s="6" t="n"/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Exactly the story-watching habit (note overlap with doi_thoi_quen-relationships)</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="49" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
@@ -3553,8 +3833,16 @@
       </c>
       <c r="O37" s="5" t="inlineStr"/>
       <c r="P37" s="5" t="inlineStr"/>
-      <c r="Q37" s="6" t="n"/>
-      <c r="R37" s="6" t="n"/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Numbers flat after six weeks = ineffective; B is a focus problem</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="49" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
@@ -3629,8 +3917,16 @@
       </c>
       <c r="O38" s="5" t="inlineStr"/>
       <c r="P38" s="5" t="inlineStr"/>
-      <c r="Q38" s="6" t="n"/>
-      <c r="R38" s="6" t="n"/>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Group-level observable; B has racing heart</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="34" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
@@ -3705,8 +4001,16 @@
       </c>
       <c r="O39" s="5" t="inlineStr"/>
       <c r="P39" s="5" t="inlineStr"/>
-      <c r="Q39" s="6" t="n"/>
-      <c r="R39" s="6" t="n"/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Clock at 8pm, two emails left: exact</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="34" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
@@ -3781,8 +4085,16 @@
       </c>
       <c r="O40" s="5" t="inlineStr"/>
       <c r="P40" s="5" t="inlineStr"/>
-      <c r="Q40" s="6" t="n"/>
-      <c r="R40" s="6" t="n"/>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Shows the forced 5am alarm directly</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="94" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
@@ -3863,8 +4175,16 @@
 self_care (Bản thân): Câu đổi việc vì bản thân được chấm về Công việc / Năng lượng.</t>
         </is>
       </c>
-      <c r="Q41" s="6" t="n"/>
-      <c r="R41" s="6" t="n"/>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Saving job posts at lunch: concrete</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="49" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
@@ -3939,8 +4259,16 @@
       </c>
       <c r="O42" s="5" t="inlineStr"/>
       <c r="P42" s="5" t="inlineStr"/>
-      <c r="Q42" s="6" t="n"/>
-      <c r="R42" s="6" t="n"/>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Offer with deadline fits stay/move choice</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="49" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
@@ -4019,8 +4347,16 @@
         </is>
       </c>
       <c r="P43" s="5" t="inlineStr"/>
-      <c r="Q43" s="6" t="n"/>
-      <c r="R43" s="6" t="n"/>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Observable routine; A is an inner dread feeling, closer to mental-health territory</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="64" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
@@ -4100,8 +4436,16 @@
 self_care (Bản thân): Xin góp ý về bản thân rơi về Giao tiếp / Một chuyện.</t>
         </is>
       </c>
-      <c r="Q44" s="6" t="n"/>
-      <c r="R44" s="6" t="n"/>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Only you have read the plan; B already got feedback</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="49" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
@@ -4176,8 +4520,16 @@
       </c>
       <c r="O45" s="5" t="inlineStr"/>
       <c r="P45" s="5" t="inlineStr"/>
-      <c r="Q45" s="6" t="n"/>
-      <c r="R45" s="6" t="n"/>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. You reaching toward your friend = seeking opinion (unsure, A also OK)</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="34" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
@@ -4252,8 +4604,16 @@
       </c>
       <c r="O46" s="5" t="inlineStr"/>
       <c r="P46" s="5" t="inlineStr"/>
-      <c r="Q46" s="6" t="n"/>
-      <c r="R46" s="6" t="n"/>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Nobody else has opened the file: exact; shorter</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="34" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
@@ -4328,8 +4688,16 @@
       </c>
       <c r="O47" s="5" t="inlineStr"/>
       <c r="P47" s="5" t="inlineStr"/>
-      <c r="Q47" s="6" t="n"/>
-      <c r="R47" s="6" t="n"/>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. "ổn đó" with no detail = need for feedback; B is judgmental</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="79" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
@@ -4409,8 +4777,16 @@
 communication (Giao tiếp): Nghỉ ngơi không thuộc giao tiếp; câu xin nghỉ có chữ nhắn/nói sẽ khớp nhãn khác.</t>
         </is>
       </c>
-      <c r="Q48" s="6" t="n"/>
-      <c r="R48" s="6" t="n"/>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Shows need and behaviour (adding tasks while yawning)</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="34" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
@@ -4485,8 +4861,16 @@
       </c>
       <c r="O49" s="5" t="inlineStr"/>
       <c r="P49" s="5" t="inlineStr"/>
-      <c r="Q49" s="6" t="n"/>
-      <c r="R49" s="6" t="n"/>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Empty Monday after three weekends fits "xin nghỉ một ngày"</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="34" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
@@ -4561,8 +4945,16 @@
       </c>
       <c r="O50" s="5" t="inlineStr"/>
       <c r="P50" s="5" t="inlineStr"/>
-      <c r="Q50" s="6" t="n"/>
-      <c r="R50" s="6" t="n"/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Shorter, observable</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="34" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
@@ -4637,8 +5029,16 @@
       </c>
       <c r="O51" s="5" t="inlineStr"/>
       <c r="P51" s="5" t="inlineStr"/>
-      <c r="Q51" s="6" t="n"/>
-      <c r="R51" s="6" t="n"/>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Laptop vs uneaten dinner = rest vs extra work</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="64" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
@@ -4718,8 +5118,16 @@
 self_care (Bản thân): Gửi đi không gắn với chăm mình.</t>
         </is>
       </c>
-      <c r="Q52" s="6" t="n"/>
-      <c r="R52" s="6" t="n"/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Email draft is more natural than a stamped paper letter for the age group</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="49" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
@@ -4794,8 +5202,16 @@
       </c>
       <c r="O53" s="5" t="inlineStr"/>
       <c r="P53" s="5" t="inlineStr"/>
-      <c r="Q53" s="6" t="n"/>
-      <c r="R53" s="6" t="n"/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Shorter, warm; gift ready, birthday tomorrow</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="34" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
@@ -4870,8 +5286,16 @@
       </c>
       <c r="O54" s="5" t="inlineStr"/>
       <c r="P54" s="5" t="inlineStr"/>
-      <c r="Q54" s="6" t="n"/>
-      <c r="R54" s="6" t="n"/>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Cursor on send: vivid; A repeats reread-N-times motif</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="34" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
@@ -4946,8 +5370,16 @@
       </c>
       <c r="O55" s="5" t="inlineStr"/>
       <c r="P55" s="5" t="inlineStr"/>
-      <c r="Q55" s="6" t="n"/>
-      <c r="R55" s="6" t="n"/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Three-screen unsent message: exact</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="79" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
@@ -5027,8 +5459,16 @@
 self_care (Bản thân): “Xin lỗi bản thân” không phải hành động quan sát được; tránh viết cảnh tự trách.</t>
         </is>
       </c>
-      <c r="Q56" s="6" t="n"/>
-      <c r="R56" s="6" t="n"/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Exact late-arrival scene</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="49" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
@@ -5107,8 +5547,16 @@
         </is>
       </c>
       <c r="P57" s="5" t="inlineStr"/>
-      <c r="Q57" s="6" t="n"/>
-      <c r="R57" s="6" t="n"/>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Works for the original bug question (any conversation); B assumes living together</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="49" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
@@ -5183,8 +5631,16 @@
       </c>
       <c r="O58" s="5" t="inlineStr"/>
       <c r="P58" s="5" t="inlineStr"/>
-      <c r="Q58" s="6" t="n"/>
-      <c r="R58" s="6" t="n"/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete consequence of the delay</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="49" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
@@ -5259,8 +5715,16 @@
       </c>
       <c r="O59" s="5" t="inlineStr"/>
       <c r="P59" s="5" t="inlineStr"/>
-      <c r="Q59" s="6" t="n"/>
-      <c r="R59" s="6" t="n"/>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. "tại vì" longer than the apology: exact, light</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="64" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
@@ -5340,8 +5804,16 @@
 self_care (Bản thân): Hẹn gặp cho mình khớp nhãn ra ngoài / chia sẻ.</t>
         </is>
       </c>
-      <c r="Q60" s="6" t="n"/>
-      <c r="R60" s="6" t="n"/>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Friend back in town, chat stopped last year: matches</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="49" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
@@ -5416,8 +5888,16 @@
       </c>
       <c r="O61" s="5" t="inlineStr"/>
       <c r="P61" s="5" t="inlineStr"/>
-      <c r="Q61" s="6" t="n"/>
-      <c r="R61" s="6" t="n"/>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete, warm; B repeats typed-deleted motif</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="49" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
@@ -5492,8 +5972,16 @@
       </c>
       <c r="O62" s="5" t="inlineStr"/>
       <c r="P62" s="5" t="inlineStr"/>
-      <c r="Q62" s="6" t="n"/>
-      <c r="R62" s="6" t="n"/>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Twelfth email, still misunderstanding: exact</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="49" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
@@ -5568,8 +6056,16 @@
       </c>
       <c r="O63" s="5" t="inlineStr"/>
       <c r="P63" s="5" t="inlineStr"/>
-      <c r="Q63" s="6" t="n"/>
-      <c r="R63" s="6" t="n"/>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Shrinking replies over two hours: fits meeting instead of texting</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="49" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
@@ -5652,8 +6148,16 @@
           <t>energy (Năng lượng): Kể với ai đó mình mệt trùng Bản thân / nhờ giúp; dùng dòng Bản thân.</t>
         </is>
       </c>
-      <c r="Q64" s="6" t="n"/>
-      <c r="R64" s="6" t="n"/>
+      <c r="Q64" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Saying "chưa có" though known: exact, non-judgmental</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="49" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
@@ -5728,8 +6232,16 @@
       </c>
       <c r="O65" s="5" t="inlineStr"/>
       <c r="P65" s="5" t="inlineStr"/>
-      <c r="Q65" s="6" t="n"/>
-      <c r="R65" s="6" t="n"/>
+      <c r="Q65" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R65" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Partner asks, you say "bình thường": matches</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="34" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
@@ -5804,8 +6316,16 @@
       </c>
       <c r="O66" s="5" t="inlineStr"/>
       <c r="P66" s="5" t="inlineStr"/>
-      <c r="Q66" s="6" t="n"/>
-      <c r="R66" s="6" t="n"/>
+      <c r="Q66" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R66" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Six tasks due Friday, still "em ổn": exact</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="49" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
@@ -5880,8 +6400,16 @@
       </c>
       <c r="O67" s="5" t="inlineStr"/>
       <c r="P67" s="5" t="inlineStr"/>
-      <c r="Q67" s="6" t="n"/>
-      <c r="R67" s="6" t="n"/>
+      <c r="Q67" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R67" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Shorter, observable; A implies something serious "chuyện gì đang xảy ra"</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="34" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
@@ -5956,8 +6484,16 @@
       </c>
       <c r="O68" s="5" t="inlineStr"/>
       <c r="P68" s="5" t="inlineStr"/>
-      <c r="Q68" s="6" t="n"/>
-      <c r="R68" s="6" t="n"/>
+      <c r="Q68" s="6" t="inlineStr">
+        <is>
+          <t>Sửa</t>
+        </is>
+      </c>
+      <c r="R68" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: viết lại → Cả tuần bạn trả lời mọi lời hỏi thăm bằng “mình ổn”, trong khi chuyện làm bạn bận lòng vẫn chưa kể với ai. (A ends in a dark room alone (heavy for a calm app); B is writing, not sharing). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="49" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
@@ -6032,8 +6568,16 @@
       </c>
       <c r="O69" s="5" t="inlineStr"/>
       <c r="P69" s="5" t="inlineStr"/>
-      <c r="Q69" s="6" t="n"/>
-      <c r="R69" s="6" t="n"/>
+      <c r="Q69" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R69" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Salary question at a party, awkward smile: vivid</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="64" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
@@ -6112,8 +6656,16 @@
         </is>
       </c>
       <c r="P70" s="5" t="inlineStr"/>
-      <c r="Q70" s="6" t="n"/>
-      <c r="R70" s="6" t="n"/>
+      <c r="Q70" s="6" t="inlineStr">
+        <is>
+          <t>Bỏ</t>
+        </is>
+      </c>
+      <c r="R70" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: Gần với kiểm soát trong quan hệ; tạm dùng cảnh general cho tới khi có lớp an toàn</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="49" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
@@ -6188,8 +6740,16 @@
       </c>
       <c r="O71" s="5" t="inlineStr"/>
       <c r="P71" s="5" t="inlineStr"/>
-      <c r="Q71" s="6" t="n"/>
-      <c r="R71" s="6" t="n"/>
+      <c r="Q71" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R71" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. A has a family dinner at 10pm (implausible); B exact</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="34" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
@@ -6264,8 +6824,16 @@
       </c>
       <c r="O72" s="5" t="inlineStr"/>
       <c r="P72" s="5" t="inlineStr"/>
-      <c r="Q72" s="6" t="n"/>
-      <c r="R72" s="6" t="n"/>
+      <c r="Q72" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R72" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Shorter, common boundary case</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="34" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
@@ -6340,8 +6908,16 @@
       </c>
       <c r="O73" s="5" t="inlineStr"/>
       <c r="P73" s="5" t="inlineStr"/>
-      <c r="Q73" s="6" t="n"/>
-      <c r="R73" s="6" t="n"/>
+      <c r="Q73" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R73" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Shows the energy cost (asleep on sofa)</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="34" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
@@ -6416,8 +6992,16 @@
       </c>
       <c r="O74" s="5" t="inlineStr"/>
       <c r="P74" s="5" t="inlineStr"/>
-      <c r="Q74" s="6" t="n"/>
-      <c r="R74" s="6" t="n"/>
+      <c r="Q74" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R74" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Shows the effect after each meeting (unsure: mirror may touch body image)</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="94" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
@@ -6498,8 +7082,16 @@
 self_care (Bản thân): Kết thúc vì bản thân trùng nhãn dừng lại / đặt ranh giới.</t>
         </is>
       </c>
-      <c r="Q75" s="6" t="n"/>
-      <c r="R75" s="6" t="n"/>
+      <c r="Q75" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R75" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Shorter, personal (only one still reminding)</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="49" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
@@ -6578,8 +7170,16 @@
         </is>
       </c>
       <c r="P76" s="5" t="inlineStr"/>
-      <c r="Q76" s="6" t="n"/>
-      <c r="R76" s="6" t="n"/>
+      <c r="Q76" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R76" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Factual, neutral on breaking up; matches question</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="34" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
@@ -6654,8 +7254,16 @@
       </c>
       <c r="O77" s="5" t="inlineStr"/>
       <c r="P77" s="5" t="inlineStr"/>
-      <c r="Q77" s="6" t="n"/>
-      <c r="R77" s="6" t="n"/>
+      <c r="Q77" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R77" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete; B exaggerates ("nhiều hơn mọi việc khác")</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="34" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
@@ -6734,8 +7342,16 @@
           <t>energy (Năng lượng): Thử lại khi đang mệt hiếm; câu rơi về Bản thân / Một chuyện.</t>
         </is>
       </c>
-      <c r="Q78" s="6" t="n"/>
-      <c r="R78" s="6" t="n"/>
+      <c r="Q78" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R78" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Old result plus new registration: exact</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="34" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
@@ -6814,8 +7430,16 @@
         </is>
       </c>
       <c r="P79" s="5" t="inlineStr"/>
-      <c r="Q79" s="6" t="n"/>
-      <c r="R79" s="6" t="n"/>
+      <c r="Q79" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R79" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Shorter, common case; no promise of reuniting</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="49" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
@@ -6890,8 +7514,16 @@
       </c>
       <c r="O80" s="5" t="inlineStr"/>
       <c r="P80" s="5" t="inlineStr"/>
-      <c r="Q80" s="6" t="n"/>
-      <c r="R80" s="6" t="n"/>
+      <c r="Q80" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R80" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Same role reposted: exact</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="49" customHeight="1">
       <c r="A81" s="5" t="inlineStr">
@@ -6966,8 +7598,16 @@
       </c>
       <c r="O81" s="5" t="inlineStr"/>
       <c r="P81" s="5" t="inlineStr"/>
-      <c r="Q81" s="6" t="n"/>
-      <c r="R81" s="6" t="n"/>
+      <c r="Q81" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R81" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Other person asks back the same thing: shows not understood</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="49" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
@@ -7042,8 +7682,16 @@
       </c>
       <c r="O82" s="5" t="inlineStr"/>
       <c r="P82" s="5" t="inlineStr"/>
-      <c r="Q82" s="6" t="n"/>
-      <c r="R82" s="6" t="n"/>
+      <c r="Q82" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R82" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Three nights then relapse: exact</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="94" customHeight="1">
       <c r="A83" s="5" t="inlineStr">
@@ -7124,8 +7772,16 @@
 energy (Năng lượng): Học thêm không gắn với năng lượng.</t>
         </is>
       </c>
-      <c r="Q83" s="6" t="n"/>
-      <c r="R83" s="6" t="n"/>
+      <c r="Q83" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R83" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Joyful sign of interest; A frames a broken streak</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="34" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
@@ -7200,8 +7856,16 @@
       </c>
       <c r="O84" s="5" t="inlineStr"/>
       <c r="P84" s="5" t="inlineStr"/>
-      <c r="Q84" s="6" t="n"/>
-      <c r="R84" s="6" t="n"/>
+      <c r="Q84" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R84" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Fits current job; B is about another job posting</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="34" customHeight="1">
       <c r="A85" s="5" t="inlineStr">
@@ -7276,8 +7940,16 @@
       </c>
       <c r="O85" s="5" t="inlineStr"/>
       <c r="P85" s="5" t="inlineStr"/>
-      <c r="Q85" s="6" t="n"/>
-      <c r="R85" s="6" t="n"/>
+      <c r="Q85" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R85" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Joyful, matches "chỉ vì thích"</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="64" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
@@ -7357,8 +8029,16 @@
 communication (Giao tiếp): Tập trung khi nghe khớp nhãn hỏi lại / nói ra.</t>
         </is>
       </c>
-      <c r="Q86" s="6" t="n"/>
-      <c r="R86" s="6" t="n"/>
+      <c r="Q86" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R86" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Exact reading-distraction scene</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="34" customHeight="1">
       <c r="A87" s="5" t="inlineStr">
@@ -7433,8 +8113,16 @@
       </c>
       <c r="O87" s="5" t="inlineStr"/>
       <c r="P87" s="5" t="inlineStr"/>
-      <c r="Q87" s="6" t="n"/>
-      <c r="R87" s="6" t="n"/>
+      <c r="Q87" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R87" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Twelve tabs across three projects: concrete</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="34" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
@@ -7509,8 +8197,16 @@
       </c>
       <c r="O88" s="5" t="inlineStr"/>
       <c r="P88" s="5" t="inlineStr"/>
-      <c r="Q88" s="6" t="n"/>
-      <c r="R88" s="6" t="n"/>
+      <c r="Q88" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R88" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete afternoon slump</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="34" customHeight="1">
       <c r="A89" s="5" t="inlineStr">
@@ -7585,8 +8281,16 @@
       </c>
       <c r="O89" s="5" t="inlineStr"/>
       <c r="P89" s="5" t="inlineStr"/>
-      <c r="Q89" s="6" t="n"/>
-      <c r="R89" s="6" t="n"/>
+      <c r="Q89" s="6" t="inlineStr">
+        <is>
+          <t>Bỏ</t>
+        </is>
+      </c>
+      <c r="R89" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: Câu hỏi mẫu là 'tập trung vào bản thân', không phải tập trung làm việc; dùng cảnh general, ghi việc tiếp theo cho T01</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="34" customHeight="1">
       <c r="A90" s="5" t="inlineStr">
@@ -7665,8 +8369,16 @@
           <t>communication (Giao tiếp): Sắp xếp lại lời nói khớp nhãn viết ra / nói ra.</t>
         </is>
       </c>
-      <c r="Q90" s="6" t="n"/>
-      <c r="R90" s="6" t="n"/>
+      <c r="Q90" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R90" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Wednesday crowded, Friday empty: exact</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="34" customHeight="1">
       <c r="A91" s="5" t="inlineStr">
@@ -7741,8 +8453,16 @@
       </c>
       <c r="O91" s="5" t="inlineStr"/>
       <c r="P91" s="5" t="inlineStr"/>
-      <c r="Q91" s="6" t="n"/>
-      <c r="R91" s="6" t="n"/>
+      <c r="Q91" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R91" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Date vs deadline clash: concrete</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="49" customHeight="1">
       <c r="A92" s="5" t="inlineStr">
@@ -7817,8 +8537,16 @@
       </c>
       <c r="O92" s="5" t="inlineStr"/>
       <c r="P92" s="5" t="inlineStr"/>
-      <c r="Q92" s="6" t="n"/>
-      <c r="R92" s="6" t="n"/>
+      <c r="Q92" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R92" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Three deadlines, list by arrival order: exact</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="34" customHeight="1">
       <c r="A93" s="5" t="inlineStr">
@@ -7893,8 +8621,16 @@
       </c>
       <c r="O93" s="5" t="inlineStr"/>
       <c r="P93" s="5" t="inlineStr"/>
-      <c r="Q93" s="6" t="n"/>
-      <c r="R93" s="6" t="n"/>
+      <c r="Q93" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R93" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete sleep schedule</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="34" customHeight="1">
       <c r="A94" s="5" t="inlineStr">
@@ -7969,8 +8705,16 @@
       </c>
       <c r="O94" s="5" t="inlineStr"/>
       <c r="P94" s="5" t="inlineStr"/>
-      <c r="Q94" s="6" t="n"/>
-      <c r="R94" s="6" t="n"/>
+      <c r="Q94" s="6" t="inlineStr">
+        <is>
+          <t>Bỏ</t>
+        </is>
+      </c>
+      <c r="R94" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: Câu hỏi mẫu là dọn phòng, gần don_dep hơn; dùng cảnh general, ghi việc tiếp theo cho T01</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="49" customHeight="1">
       <c r="A95" s="5" t="inlineStr">
@@ -8049,8 +8793,16 @@
           <t>communication (Giao tiếp): Nhờ người nói giúp dễ thành nói thay người khác; tránh.</t>
         </is>
       </c>
-      <c r="Q95" s="6" t="n"/>
-      <c r="R95" s="6" t="n"/>
+      <c r="Q95" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R95" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Helper list only your name: exact</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="34" customHeight="1">
       <c r="A96" s="5" t="inlineStr">
@@ -8125,8 +8877,16 @@
       </c>
       <c r="O96" s="5" t="inlineStr"/>
       <c r="P96" s="5" t="inlineStr"/>
-      <c r="Q96" s="6" t="n"/>
-      <c r="R96" s="6" t="n"/>
+      <c r="Q96" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R96" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Observable imbalance; B chart already exists</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="49" customHeight="1">
       <c r="A97" s="5" t="inlineStr">
@@ -8201,8 +8961,16 @@
       </c>
       <c r="O97" s="5" t="inlineStr"/>
       <c r="P97" s="5" t="inlineStr"/>
-      <c r="Q97" s="6" t="n"/>
-      <c r="R97" s="6" t="n"/>
+      <c r="Q97" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R97" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete cost of doing it alone</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="34" customHeight="1">
       <c r="A98" s="5" t="inlineStr">
@@ -8277,8 +9045,16 @@
       </c>
       <c r="O98" s="5" t="inlineStr"/>
       <c r="P98" s="5" t="inlineStr"/>
-      <c r="Q98" s="6" t="n"/>
-      <c r="R98" s="6" t="n"/>
+      <c r="Q98" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R98" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="64" customHeight="1">
       <c r="A99" s="5" t="inlineStr">
@@ -8357,8 +9133,16 @@
         </is>
       </c>
       <c r="P99" s="5" t="inlineStr"/>
-      <c r="Q99" s="6" t="n"/>
-      <c r="R99" s="6" t="n"/>
+      <c r="Q99" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R99" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Lighter, observable; A is several nights alone in a room (heavy)</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="64" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
@@ -8438,8 +9222,16 @@
 self_care (Bản thân): Góp ý cho bản thân dễ thành tự chê; tránh.</t>
         </is>
       </c>
-      <c r="Q100" s="6" t="n"/>
-      <c r="R100" s="6" t="n"/>
+      <c r="Q100" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R100" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Group already hearting it shows why feedback is hard; B also good</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="34" customHeight="1">
       <c r="A101" s="5" t="inlineStr">
@@ -8514,8 +9306,16 @@
       </c>
       <c r="O101" s="5" t="inlineStr"/>
       <c r="P101" s="5" t="inlineStr"/>
-      <c r="Q101" s="6" t="n"/>
-      <c r="R101" s="6" t="n"/>
+      <c r="Q101" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R101" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Shows recurrence ("lần thứ ba")</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="34" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
@@ -8590,8 +9390,16 @@
       </c>
       <c r="O102" s="5" t="inlineStr"/>
       <c r="P102" s="5" t="inlineStr"/>
-      <c r="Q102" s="6" t="n"/>
-      <c r="R102" s="6" t="n"/>
+      <c r="Q102" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R102" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Old data, presentation tomorrow: exact</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="34" customHeight="1">
       <c r="A103" s="5" t="inlineStr">
@@ -8666,8 +9474,16 @@
       </c>
       <c r="O103" s="5" t="inlineStr"/>
       <c r="P103" s="5" t="inlineStr"/>
-      <c r="Q103" s="6" t="n"/>
-      <c r="R103" s="6" t="n"/>
+      <c r="Q103" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R103" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. "ổn mà" while circling three spots: exact dilemma</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="64" customHeight="1">
       <c r="A104" s="5" t="inlineStr">
@@ -8747,8 +9563,16 @@
 self_care (Bản thân): Đề xuất cho bản thân không phải hành động hướng ra người khác.</t>
         </is>
       </c>
-      <c r="Q104" s="6" t="n"/>
-      <c r="R104" s="6" t="n"/>
+      <c r="Q104" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R104" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Alternative plan ready in notes: exact</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="49" customHeight="1">
       <c r="A105" s="5" t="inlineStr">
@@ -8823,8 +9647,16 @@
       </c>
       <c r="O105" s="5" t="inlineStr"/>
       <c r="P105" s="5" t="inlineStr"/>
-      <c r="Q105" s="6" t="n"/>
-      <c r="R105" s="6" t="n"/>
+      <c r="Q105" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R105" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. A grammar awkward ("câu trả lời thường có khi…")</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="49" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
@@ -8899,8 +9731,16 @@
       </c>
       <c r="O106" s="5" t="inlineStr"/>
       <c r="P106" s="5" t="inlineStr"/>
-      <c r="Q106" s="6" t="n"/>
-      <c r="R106" s="6" t="n"/>
+      <c r="Q106" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R106" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Template already built: exact</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="49" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
@@ -8975,8 +9815,16 @@
       </c>
       <c r="O107" s="5" t="inlineStr"/>
       <c r="P107" s="5" t="inlineStr"/>
-      <c r="Q107" s="6" t="n"/>
-      <c r="R107" s="6" t="n"/>
+      <c r="Q107" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R107" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Others spoke first: matches being cut off</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="64" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
@@ -9056,8 +9904,16 @@
 communication (Giao tiếp): Dọn dẹp không thuộc giao tiếp.</t>
         </is>
       </c>
-      <c r="Q108" s="6" t="n"/>
-      <c r="R108" s="6" t="n"/>
+      <c r="Q108" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R108" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Chair as clothes rack: vivid</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="49" customHeight="1">
       <c r="A109" s="5" t="inlineStr">
@@ -9132,8 +9988,16 @@
       </c>
       <c r="O109" s="5" t="inlineStr"/>
       <c r="P109" s="5" t="inlineStr"/>
-      <c r="Q109" s="6" t="n"/>
-      <c r="R109" s="6" t="n"/>
+      <c r="Q109" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R109" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Physical desk matches question</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="34" customHeight="1">
       <c r="A110" s="5" t="inlineStr">
@@ -9208,8 +10072,16 @@
       </c>
       <c r="O110" s="5" t="inlineStr"/>
       <c r="P110" s="5" t="inlineStr"/>
-      <c r="Q110" s="6" t="n"/>
-      <c r="R110" s="6" t="n"/>
+      <c r="Q110" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R110" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete; B facing the wall is gloomier</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="34" customHeight="1">
       <c r="A111" s="5" t="inlineStr">
@@ -9284,8 +10156,16 @@
       </c>
       <c r="O111" s="5" t="inlineStr"/>
       <c r="P111" s="5" t="inlineStr"/>
-      <c r="Q111" s="6" t="n"/>
-      <c r="R111" s="6" t="n"/>
+      <c r="Q111" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R111" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Loved reading corner buried: warm</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="64" customHeight="1">
       <c r="A112" s="5" t="inlineStr">
@@ -9365,8 +10245,16 @@
 communication (Giao tiếp): Ra ngoài không thuộc giao tiếp.</t>
         </is>
       </c>
-      <c r="Q112" s="6" t="n"/>
-      <c r="R112" s="6" t="n"/>
+      <c r="Q112" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R112" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Two weekends bed-to-desk: concrete</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="34" customHeight="1">
       <c r="A113" s="5" t="inlineStr">
@@ -9441,8 +10329,16 @@
       </c>
       <c r="O113" s="5" t="inlineStr"/>
       <c r="P113" s="5" t="inlineStr"/>
-      <c r="Q113" s="6" t="n"/>
-      <c r="R113" s="6" t="n"/>
+      <c r="Q113" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R113" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Everyone hearted but you: exact</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="34" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
@@ -9517,8 +10413,16 @@
       </c>
       <c r="O114" s="5" t="inlineStr"/>
       <c r="P114" s="5" t="inlineStr"/>
-      <c r="Q114" s="6" t="n"/>
-      <c r="R114" s="6" t="n"/>
+      <c r="Q114" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R114" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Warm, gentle light through curtain; A also fine</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="34" customHeight="1">
       <c r="A115" s="5" t="inlineStr">
@@ -9593,8 +10497,16 @@
       </c>
       <c r="O115" s="5" t="inlineStr"/>
       <c r="P115" s="5" t="inlineStr"/>
-      <c r="Q115" s="6" t="n"/>
-      <c r="R115" s="6" t="n"/>
+      <c r="Q115" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R115" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Shows the "alone" part (checking who can come)</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="64" customHeight="1">
       <c r="A116" s="5" t="inlineStr">
@@ -9674,8 +10586,16 @@
 communication (Giao tiếp): Ở nhà không thuộc giao tiếp.</t>
         </is>
       </c>
-      <c r="Q116" s="6" t="n"/>
-      <c r="R116" s="6" t="n"/>
+      <c r="Q116" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R116" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Already in pyjamas: vivid</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="49" customHeight="1">
       <c r="A117" s="5" t="inlineStr">
@@ -9750,8 +10670,16 @@
       </c>
       <c r="O117" s="5" t="inlineStr"/>
       <c r="P117" s="5" t="inlineStr"/>
-      <c r="Q117" s="6" t="n"/>
-      <c r="R117" s="6" t="n"/>
+      <c r="Q117" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R117" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Fits cooking at home</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="34" customHeight="1">
       <c r="A118" s="5" t="inlineStr">
@@ -9826,8 +10754,16 @@
       </c>
       <c r="O118" s="5" t="inlineStr"/>
       <c r="P118" s="5" t="inlineStr"/>
-      <c r="Q118" s="6" t="n"/>
-      <c r="R118" s="6" t="n"/>
+      <c r="Q118" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R118" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete fatigue after six days</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="34" customHeight="1">
       <c r="A119" s="5" t="inlineStr">
@@ -9902,8 +10838,16 @@
       </c>
       <c r="O119" s="5" t="inlineStr"/>
       <c r="P119" s="5" t="inlineStr"/>
-      <c r="Q119" s="6" t="n"/>
-      <c r="R119" s="6" t="n"/>
+      <c r="Q119" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R119" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Muting phone at the door: exact</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="34" customHeight="1">
       <c r="A120" s="5" t="inlineStr">
@@ -9982,8 +10926,16 @@
           <t>communication (Giao tiếp): Đổi thói quen nói chuyện khớp nhãn nói ra / hỏi lại.</t>
         </is>
       </c>
-      <c r="Q120" s="6" t="n"/>
-      <c r="R120" s="6" t="n"/>
+      <c r="Q120" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R120" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Shows the repeated promise, matches DC-10 "đã hứa"</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="34" customHeight="1">
       <c r="A121" s="5" t="inlineStr">
@@ -10058,8 +11010,16 @@
       </c>
       <c r="O121" s="5" t="inlineStr"/>
       <c r="P121" s="5" t="inlineStr"/>
-      <c r="Q121" s="6" t="n"/>
-      <c r="R121" s="6" t="n"/>
+      <c r="Q121" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R121" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Subtle, concrete (near-duplicate of dung_lai-relationships)</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="49" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
@@ -10134,8 +11094,16 @@
       </c>
       <c r="O122" s="5" t="inlineStr"/>
       <c r="P122" s="5" t="inlineStr"/>
-      <c r="Q122" s="6" t="n"/>
-      <c r="R122" s="6" t="n"/>
+      <c r="Q122" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R122" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Opening work email mid-movie shows the habit</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="64" customHeight="1">
       <c r="A123" s="5" t="inlineStr">
@@ -10214,8 +11182,16 @@
         </is>
       </c>
       <c r="P123" s="5" t="inlineStr"/>
-      <c r="Q123" s="6" t="n"/>
-      <c r="R123" s="6" t="n"/>
+      <c r="Q123" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R123" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. A pairs coffee with 1am wakefulness = health claim; B safe</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="34" customHeight="1">
       <c r="A124" s="5" t="inlineStr">
@@ -10290,8 +11266,16 @@
       </c>
       <c r="O124" s="5" t="inlineStr"/>
       <c r="P124" s="5" t="inlineStr"/>
-      <c r="Q124" s="6" t="n"/>
-      <c r="R124" s="6" t="n"/>
+      <c r="Q124" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R124" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Joyful (tree in bloom), observable</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="64" customHeight="1">
       <c r="A125" s="5" t="inlineStr">
@@ -10371,8 +11355,16 @@
 communication (Giao tiếp): Tự thưởng không thuộc giao tiếp.</t>
         </is>
       </c>
-      <c r="Q125" s="6" t="n"/>
-      <c r="R125" s="6" t="n"/>
+      <c r="Q125" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R125" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Shows the missing celebration; B nudges a purchase</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="34" customHeight="1">
       <c r="A126" s="5" t="inlineStr">
@@ -10447,8 +11439,16 @@
       </c>
       <c r="O126" s="5" t="inlineStr"/>
       <c r="P126" s="5" t="inlineStr"/>
-      <c r="Q126" s="6" t="n"/>
-      <c r="R126" s="6" t="n"/>
+      <c r="Q126" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R126" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Opening the next task immediately: exact</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="34" customHeight="1">
       <c r="A127" s="5" t="inlineStr">
@@ -10523,8 +11523,16 @@
       </c>
       <c r="O127" s="5" t="inlineStr"/>
       <c r="P127" s="5" t="inlineStr"/>
-      <c r="Q127" s="6" t="n"/>
-      <c r="R127" s="6" t="n"/>
+      <c r="Q127" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R127" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Energy row: shows tiredness</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="34" customHeight="1">
       <c r="A128" s="5" t="inlineStr">
@@ -10599,8 +11607,16 @@
       </c>
       <c r="O128" s="5" t="inlineStr"/>
       <c r="P128" s="5" t="inlineStr"/>
-      <c r="Q128" s="6" t="n"/>
-      <c r="R128" s="6" t="n"/>
+      <c r="Q128" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R128" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Shorter, "cũng may thôi" is exactly self-dismissal</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="34" customHeight="1">
       <c r="A129" s="5" t="inlineStr">
@@ -10675,8 +11691,16 @@
       </c>
       <c r="O129" s="5" t="inlineStr"/>
       <c r="P129" s="5" t="inlineStr"/>
-      <c r="Q129" s="6" t="n"/>
-      <c r="R129" s="6" t="n"/>
+      <c r="Q129" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R129" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Opened phone three times, forgot why: concrete</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="49" customHeight="1">
       <c r="A130" s="5" t="inlineStr">
@@ -10751,8 +11775,16 @@
       </c>
       <c r="O130" s="5" t="inlineStr"/>
       <c r="P130" s="5" t="inlineStr"/>
-      <c r="Q130" s="6" t="n"/>
-      <c r="R130" s="6" t="n"/>
+      <c r="Q130" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R130" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Forgot the main point last time: exact</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="34" customHeight="1">
       <c r="A131" s="5" t="inlineStr">
@@ -10827,8 +11859,16 @@
       </c>
       <c r="O131" s="5" t="inlineStr"/>
       <c r="P131" s="5" t="inlineStr"/>
-      <c r="Q131" s="6" t="n"/>
-      <c r="R131" s="6" t="n"/>
+      <c r="Q131" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R131" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Only remembering two things at review: exact</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="34" customHeight="1">
       <c r="A132" s="5" t="inlineStr">
@@ -10903,8 +11943,16 @@
       </c>
       <c r="O132" s="5" t="inlineStr"/>
       <c r="P132" s="5" t="inlineStr"/>
-      <c r="Q132" s="6" t="n"/>
-      <c r="R132" s="6" t="n"/>
+      <c r="Q132" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R132" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. About the upcoming meeting ("trước")</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="34" customHeight="1">
       <c r="A133" s="5" t="inlineStr">
@@ -10979,8 +12027,16 @@
       </c>
       <c r="O133" s="5" t="inlineStr"/>
       <c r="P133" s="5" t="inlineStr"/>
-      <c r="Q133" s="6" t="n"/>
-      <c r="R133" s="6" t="n"/>
+      <c r="Q133" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R133" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Cannot name what tired you: exact</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="34" customHeight="1">
       <c r="A134" s="5" t="inlineStr">
@@ -11055,8 +12111,16 @@
       </c>
       <c r="O134" s="5" t="inlineStr"/>
       <c r="P134" s="5" t="inlineStr"/>
-      <c r="Q134" s="6" t="n"/>
-      <c r="R134" s="6" t="n"/>
+      <c r="Q134" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="R134" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Joyful reason to journal</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:R134"/>
@@ -11245,8 +12309,16 @@
         </is>
       </c>
       <c r="N2" s="5" t="inlineStr"/>
-      <c r="O2" s="6" t="n"/>
-      <c r="P2" s="6" t="n"/>
+      <c r="O2" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Neutral concrete action; B is an opening line in disguise</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="49" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -11315,8 +12387,16 @@
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr"/>
-      <c r="O3" s="6" t="n"/>
-      <c r="P3" s="6" t="n"/>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Asks the missing detail = verify; B duplicates calendar check</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -11385,8 +12465,16 @@
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr"/>
-      <c r="O4" s="6" t="n"/>
-      <c r="P4" s="6" t="n"/>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete delaying line; B repeats calendar</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="49" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -11455,8 +12543,16 @@
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr"/>
-      <c r="O5" s="6" t="n"/>
-      <c r="P5" s="6" t="n"/>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete trade-off; B wording awkward</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -11525,8 +12621,16 @@
         </is>
       </c>
       <c r="N6" s="5" t="inlineStr"/>
-      <c r="O6" s="6" t="n"/>
-      <c r="P6" s="6" t="n"/>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>Sửa</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: viết lại → Mở lời: “Mình nhận nhé, mình chốt lại giờ giấc cụ thể với bạn được không?” (Both drafts are work-only (weekdays / hạn chót) but step renders for movie date, moving help, dinner). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -11595,8 +12699,16 @@
         </is>
       </c>
       <c r="N7" s="5" t="inlineStr"/>
-      <c r="O7" s="6" t="n"/>
-      <c r="P7" s="6" t="n"/>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Topic-neutral; A "không nhận được" is odd for a date/club invite</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="49" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -11665,8 +12777,16 @@
         </is>
       </c>
       <c r="N8" s="5" t="inlineStr"/>
-      <c r="O8" s="6" t="n"/>
-      <c r="P8" s="6" t="n"/>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Does the actual refusal; B swaps in a different small thing</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -11735,8 +12855,16 @@
         </is>
       </c>
       <c r="N9" s="5" t="inlineStr"/>
-      <c r="O9" s="6" t="n"/>
-      <c r="P9" s="6" t="n"/>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Topic-neutral; A "xin phép không nhận" odd for a date</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -11805,8 +12933,16 @@
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr"/>
-      <c r="O10" s="6" t="n"/>
-      <c r="P10" s="6" t="n"/>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Self-care rule: concrete decision line; A vague</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
@@ -11875,8 +13011,16 @@
         </is>
       </c>
       <c r="N11" s="5" t="inlineStr"/>
-      <c r="O11" s="6" t="n"/>
-      <c r="P11" s="6" t="n"/>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. B gives "kín lịch" reason that may be untrue; A neutral</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -11945,8 +13089,16 @@
         </is>
       </c>
       <c r="N12" s="5" t="inlineStr"/>
-      <c r="O12" s="6" t="n"/>
-      <c r="P12" s="6" t="n"/>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete "Mình thấy…" frame</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="49" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
@@ -12015,8 +13167,16 @@
         </is>
       </c>
       <c r="N13" s="5" t="inlineStr"/>
-      <c r="O13" s="6" t="n"/>
-      <c r="P13" s="6" t="n"/>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Verifies wording; A repeats focus A</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
@@ -12085,8 +13245,16 @@
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr"/>
-      <c r="O14" s="6" t="n"/>
-      <c r="P14" s="6" t="n"/>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Broader; B is meeting-only</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="49" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -12155,8 +13323,16 @@
         </is>
       </c>
       <c r="N15" s="5" t="inlineStr"/>
-      <c r="O15" s="6" t="n"/>
-      <c r="P15" s="6" t="n"/>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Concrete question; A abstract ("sự thật hay sự yên ổn")</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -12225,8 +13401,16 @@
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr"/>
-      <c r="O16" s="6" t="n"/>
-      <c r="P16" s="6" t="n"/>
+      <c r="O16" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Neutral across topics</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
@@ -12295,8 +13479,16 @@
         </is>
       </c>
       <c r="N17" s="5" t="inlineStr"/>
-      <c r="O17" s="6" t="n"/>
-      <c r="P17" s="6" t="n"/>
+      <c r="O17" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Topic-neutral; A assumes the other person sent the last message</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="49" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
@@ -12365,8 +13557,16 @@
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr"/>
-      <c r="O18" s="6" t="n"/>
-      <c r="P18" s="6" t="n"/>
+      <c r="O18" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Neutral; B "hỏi thăm" does not fit a client reply</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
@@ -12435,8 +13635,16 @@
         </is>
       </c>
       <c r="N19" s="5" t="inlineStr"/>
-      <c r="O19" s="6" t="n"/>
-      <c r="P19" s="6" t="n"/>
+      <c r="O19" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Shorter, concrete trigger</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="49" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
@@ -12505,8 +13713,16 @@
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr"/>
-      <c r="O20" s="6" t="n"/>
-      <c r="P20" s="6" t="n"/>
+      <c r="O20" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. B clunky</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="34" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
@@ -12575,8 +13791,16 @@
         </is>
       </c>
       <c r="N21" s="5" t="inlineStr"/>
-      <c r="O21" s="6" t="n"/>
-      <c r="P21" s="6" t="n"/>
+      <c r="O21" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Works for old friend/client; A is date-only</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="34" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
@@ -12645,8 +13869,16 @@
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr"/>
-      <c r="O22" s="6" t="n"/>
-      <c r="P22" s="6" t="n"/>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete sample question</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="49" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
@@ -12715,8 +13947,16 @@
         </is>
       </c>
       <c r="N23" s="5" t="inlineStr"/>
-      <c r="O23" s="6" t="n"/>
-      <c r="P23" s="6" t="n"/>
+      <c r="O23" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Paraphrase check = verify; topic-neutral</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="34" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
@@ -12785,8 +14025,16 @@
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr"/>
-      <c r="O24" s="6" t="n"/>
-      <c r="P24" s="6" t="n"/>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Natural spoken line</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="34" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
@@ -12855,8 +14103,16 @@
         </is>
       </c>
       <c r="N25" s="5" t="inlineStr"/>
-      <c r="O25" s="6" t="n"/>
-      <c r="P25" s="6" t="n"/>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Clear</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="34" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
@@ -12925,8 +14181,16 @@
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr"/>
-      <c r="O26" s="6" t="n"/>
-      <c r="P26" s="6" t="n"/>
+      <c r="O26" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Shorter, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="34" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
@@ -12995,8 +14259,16 @@
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr"/>
-      <c r="O27" s="6" t="n"/>
-      <c r="P27" s="6" t="n"/>
+      <c r="O27" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Topic-neutral; B only for chat/inbox waiting</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="49" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
@@ -13065,8 +14337,16 @@
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr"/>
-      <c r="O28" s="6" t="n"/>
-      <c r="P28" s="6" t="n"/>
+      <c r="O28" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Verify after a set time; A duplicates focus A</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="34" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
@@ -13135,8 +14415,16 @@
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr"/>
-      <c r="O29" s="6" t="n"/>
-      <c r="P29" s="6" t="n"/>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Shorter</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="34" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
@@ -13205,8 +14493,16 @@
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr"/>
-      <c r="O30" s="6" t="n"/>
-      <c r="P30" s="6" t="n"/>
+      <c r="O30" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Shorter, natural; A grammatically heavy</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="34" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
@@ -13275,8 +14571,16 @@
         </is>
       </c>
       <c r="N31" s="5" t="inlineStr"/>
-      <c r="O31" s="6" t="n"/>
-      <c r="P31" s="6" t="n"/>
+      <c r="O31" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Broader</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="34" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
@@ -13345,8 +14649,16 @@
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr"/>
-      <c r="O32" s="6" t="n"/>
-      <c r="P32" s="6" t="n"/>
+      <c r="O32" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Topic-neutral; A paint-box example</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="49" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
@@ -13415,8 +14727,16 @@
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr"/>
-      <c r="O33" s="6" t="n"/>
-      <c r="P33" s="6" t="n"/>
+      <c r="O33" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Try plus note like/hard = verify</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
@@ -13485,8 +14805,16 @@
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr"/>
-      <c r="O34" s="6" t="n"/>
-      <c r="P34" s="6" t="n"/>
+      <c r="O34" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Topic-neutral; A video-tutorial only</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="34" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
@@ -13555,8 +14883,16 @@
         </is>
       </c>
       <c r="N35" s="5" t="inlineStr"/>
-      <c r="O35" s="6" t="n"/>
-      <c r="P35" s="6" t="n"/>
+      <c r="O35" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Concrete number</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="34" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
@@ -13625,8 +14961,16 @@
         </is>
       </c>
       <c r="N36" s="5" t="inlineStr"/>
-      <c r="O36" s="6" t="n"/>
-      <c r="P36" s="6" t="n"/>
+      <c r="O36" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Natural invitation</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="34" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
@@ -13695,8 +15039,16 @@
         </is>
       </c>
       <c r="N37" s="5" t="inlineStr"/>
-      <c r="O37" s="6" t="n"/>
-      <c r="P37" s="6" t="n"/>
+      <c r="O37" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete (unsure: presupposes a set time; B is vaguer)</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="49" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
@@ -13765,8 +15117,16 @@
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr"/>
-      <c r="O38" s="6" t="n"/>
-      <c r="P38" s="6" t="n"/>
+      <c r="O38" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Shorter, topic-neutral</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="34" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
@@ -13835,8 +15195,16 @@
         </is>
       </c>
       <c r="N39" s="5" t="inlineStr"/>
-      <c r="O39" s="6" t="n"/>
-      <c r="P39" s="6" t="n"/>
+      <c r="O39" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Shorter</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="34" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
@@ -13905,8 +15273,16 @@
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr"/>
-      <c r="O40" s="6" t="n"/>
-      <c r="P40" s="6" t="n"/>
+      <c r="O40" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Self-care rule: concrete stop signal; A deliberative</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="34" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
@@ -13975,8 +15351,16 @@
         </is>
       </c>
       <c r="N41" s="5" t="inlineStr"/>
-      <c r="O41" s="6" t="n"/>
-      <c r="P41" s="6" t="n"/>
+      <c r="O41" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Shorter, fits conversation/argument</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="34" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
@@ -14045,8 +15429,16 @@
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr"/>
-      <c r="O42" s="6" t="n"/>
-      <c r="P42" s="6" t="n"/>
+      <c r="O42" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. B presupposes a saved posting</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="49" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
@@ -14115,8 +15507,16 @@
         </is>
       </c>
       <c r="N43" s="5" t="inlineStr"/>
-      <c r="O43" s="6" t="n"/>
-      <c r="P43" s="6" t="n"/>
+      <c r="O43" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete outreach</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="34" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
@@ -14185,8 +15585,16 @@
         </is>
       </c>
       <c r="N44" s="5" t="inlineStr"/>
-      <c r="O44" s="6" t="n"/>
-      <c r="P44" s="6" t="n"/>
+      <c r="O44" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Gentle, same day; B crosses to next morning</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="49" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
@@ -14255,8 +15663,16 @@
         </is>
       </c>
       <c r="N45" s="5" t="inlineStr"/>
-      <c r="O45" s="6" t="n"/>
-      <c r="P45" s="6" t="n"/>
+      <c r="O45" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete trade-off</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="34" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
@@ -14325,8 +15741,16 @@
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr"/>
-      <c r="O46" s="6" t="n"/>
-      <c r="P46" s="6" t="n"/>
+      <c r="O46" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. A opens a job-change talk with the boss (risky); B safer</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="34" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
@@ -14395,8 +15819,16 @@
         </is>
       </c>
       <c r="N47" s="5" t="inlineStr"/>
-      <c r="O47" s="6" t="n"/>
-      <c r="P47" s="6" t="n"/>
+      <c r="O47" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Topic-neutral; A "bản nháp" fails relationships topic</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="49" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
@@ -14465,8 +15897,16 @@
         </is>
       </c>
       <c r="N48" s="5" t="inlineStr"/>
-      <c r="O48" s="6" t="n"/>
-      <c r="P48" s="6" t="n"/>
+      <c r="O48" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Neutral</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="34" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
@@ -14535,8 +15975,16 @@
         </is>
       </c>
       <c r="N49" s="5" t="inlineStr"/>
-      <c r="O49" s="6" t="n"/>
-      <c r="P49" s="6" t="n"/>
+      <c r="O49" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Clear</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="34" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
@@ -14605,8 +16053,16 @@
         </is>
       </c>
       <c r="N50" s="5" t="inlineStr"/>
-      <c r="O50" s="6" t="n"/>
-      <c r="P50" s="6" t="n"/>
+      <c r="O50" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. B is about after receiving feedback</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="34" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
@@ -14675,8 +16131,16 @@
         </is>
       </c>
       <c r="N51" s="5" t="inlineStr"/>
-      <c r="O51" s="6" t="n"/>
-      <c r="P51" s="6" t="n"/>
+      <c r="O51" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Fits 3 of 4 topics; B work-only register (relationships still weak)</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="34" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
@@ -14745,8 +16209,16 @@
         </is>
       </c>
       <c r="N52" s="5" t="inlineStr"/>
-      <c r="O52" s="6" t="n"/>
-      <c r="P52" s="6" t="n"/>
+      <c r="O52" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Shorter with a real trigger (DC-02 noted missing trigger)</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="49" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
@@ -14815,8 +16287,16 @@
         </is>
       </c>
       <c r="N53" s="5" t="inlineStr"/>
-      <c r="O53" s="6" t="n"/>
-      <c r="P53" s="6" t="n"/>
+      <c r="O53" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Bản A kéo dài cả buổi tối, vượt quy tắc một việc nhỏ</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="34" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
@@ -14885,8 +16365,16 @@
         </is>
       </c>
       <c r="N54" s="5" t="inlineStr"/>
-      <c r="O54" s="6" t="n"/>
-      <c r="P54" s="6" t="n"/>
+      <c r="O54" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Topic-neutral, does the rest now</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="34" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
@@ -14955,8 +16443,16 @@
         </is>
       </c>
       <c r="N55" s="5" t="inlineStr"/>
-      <c r="O55" s="6" t="n"/>
-      <c r="P55" s="6" t="n"/>
+      <c r="O55" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Self-care rule: sets the stop time; A deliberative</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="34" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
@@ -15025,8 +16521,16 @@
         </is>
       </c>
       <c r="N56" s="5" t="inlineStr"/>
-      <c r="O56" s="6" t="n"/>
-      <c r="P56" s="6" t="n"/>
+      <c r="O56" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Broader; B work-only</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="34" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
@@ -15095,8 +16599,16 @@
         </is>
       </c>
       <c r="N57" s="5" t="inlineStr"/>
-      <c r="O57" s="6" t="n"/>
-      <c r="P57" s="6" t="n"/>
+      <c r="O57" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Shorter</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="49" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
@@ -15165,8 +16677,16 @@
         </is>
       </c>
       <c r="N58" s="5" t="inlineStr"/>
-      <c r="O58" s="6" t="n"/>
-      <c r="P58" s="6" t="n"/>
+      <c r="O58" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. B overlaps xin_gop_y</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="34" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
@@ -15235,8 +16755,16 @@
         </is>
       </c>
       <c r="N59" s="5" t="inlineStr"/>
-      <c r="O59" s="6" t="n"/>
-      <c r="P59" s="6" t="n"/>
+      <c r="O59" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Shorter</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="34" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
@@ -15305,8 +16833,16 @@
         </is>
       </c>
       <c r="N60" s="5" t="inlineStr"/>
-      <c r="O60" s="6" t="n"/>
-      <c r="P60" s="6" t="n"/>
+      <c r="O60" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Natural, fits gift too</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="34" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
@@ -15375,8 +16911,16 @@
         </is>
       </c>
       <c r="N61" s="5" t="inlineStr"/>
-      <c r="O61" s="6" t="n"/>
-      <c r="P61" s="6" t="n"/>
+      <c r="O61" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. B birthday-gift only</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="34" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
@@ -15445,8 +16989,16 @@
         </is>
       </c>
       <c r="N62" s="5" t="inlineStr"/>
-      <c r="O62" s="6" t="n"/>
-      <c r="P62" s="6" t="n"/>
+      <c r="O62" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Exact</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="49" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
@@ -15515,8 +17067,16 @@
         </is>
       </c>
       <c r="N63" s="5" t="inlineStr"/>
-      <c r="O63" s="6" t="n"/>
-      <c r="P63" s="6" t="n"/>
+      <c r="O63" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Listen before explaining</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="34" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
@@ -15585,8 +17145,16 @@
         </is>
       </c>
       <c r="N64" s="5" t="inlineStr"/>
-      <c r="O64" s="6" t="n"/>
-      <c r="P64" s="6" t="n"/>
+      <c r="O64" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Distinct path; A repeats focus A</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="34" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
@@ -15655,8 +17223,16 @@
         </is>
       </c>
       <c r="N65" s="5" t="inlineStr"/>
-      <c r="O65" s="6" t="n"/>
-      <c r="P65" s="6" t="n"/>
+      <c r="O65" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. B hints at other person readiness</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="34" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
@@ -15725,8 +17301,16 @@
         </is>
       </c>
       <c r="N66" s="5" t="inlineStr"/>
-      <c r="O66" s="6" t="n"/>
-      <c r="P66" s="6" t="n"/>
+      <c r="O66" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P66" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. B late-arrival only (A "câu mình nói" fits work delay less)</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="34" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
@@ -15795,8 +17379,16 @@
         </is>
       </c>
       <c r="N67" s="5" t="inlineStr"/>
-      <c r="O67" s="6" t="n"/>
-      <c r="P67" s="6" t="n"/>
+      <c r="O67" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P67" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Considerate</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="49" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
@@ -15865,8 +17457,16 @@
         </is>
       </c>
       <c r="N68" s="5" t="inlineStr"/>
-      <c r="O68" s="6" t="n"/>
-      <c r="P68" s="6" t="n"/>
+      <c r="O68" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P68" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Hỏi lịch rảnh làm được ngay, trong 10 phút</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="34" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
@@ -15935,8 +17535,16 @@
         </is>
       </c>
       <c r="N69" s="5" t="inlineStr"/>
-      <c r="O69" s="6" t="n"/>
-      <c r="P69" s="6" t="n"/>
+      <c r="O69" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P69" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="34" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
@@ -16005,8 +17613,16 @@
         </is>
       </c>
       <c r="N70" s="5" t="inlineStr"/>
-      <c r="O70" s="6" t="n"/>
-      <c r="P70" s="6" t="n"/>
+      <c r="O70" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P70" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Closer to choosing</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="34" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
@@ -16075,8 +17691,16 @@
         </is>
       </c>
       <c r="N71" s="5" t="inlineStr"/>
-      <c r="O71" s="6" t="n"/>
-      <c r="P71" s="6" t="n"/>
+      <c r="O71" s="6" t="inlineStr">
+        <is>
+          <t>Sửa</t>
+        </is>
+      </c>
+      <c r="P71" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: viết lại → Mở lời: “Cuối tuần này bạn rảnh không, mình đi cà phê một chút nhé?” (A "Lâu rồi không gặp" wrong for new acquaintance row; B texting-only). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="34" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
@@ -16145,8 +17769,16 @@
         </is>
       </c>
       <c r="N72" s="5" t="inlineStr"/>
-      <c r="O72" s="6" t="n"/>
-      <c r="P72" s="6" t="n"/>
+      <c r="O72" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P72" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Neutral; B assumes sadness</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="49" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
@@ -16215,8 +17847,16 @@
         </is>
       </c>
       <c r="N73" s="5" t="inlineStr"/>
-      <c r="O73" s="6" t="n"/>
-      <c r="P73" s="6" t="n"/>
+      <c r="O73" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P73" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Verify</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="34" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
@@ -16285,8 +17925,16 @@
         </is>
       </c>
       <c r="N74" s="5" t="inlineStr"/>
-      <c r="O74" s="6" t="n"/>
-      <c r="P74" s="6" t="n"/>
+      <c r="O74" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P74" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete sample</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="34" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
@@ -16355,8 +18003,16 @@
         </is>
       </c>
       <c r="N75" s="5" t="inlineStr"/>
-      <c r="O75" s="6" t="n"/>
-      <c r="P75" s="6" t="n"/>
+      <c r="O75" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P75" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Concrete trust criterion</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="34" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
@@ -16425,8 +18081,16 @@
         </is>
       </c>
       <c r="N76" s="5" t="inlineStr"/>
-      <c r="O76" s="6" t="n"/>
-      <c r="P76" s="6" t="n"/>
+      <c r="O76" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P76" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Warm, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="34" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
@@ -16495,8 +18159,16 @@
         </is>
       </c>
       <c r="N77" s="5" t="inlineStr"/>
-      <c r="O77" s="6" t="n"/>
-      <c r="P77" s="6" t="n"/>
+      <c r="O77" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P77" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Self-care rule: does it; B is preparation</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="49" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
@@ -16565,8 +18237,16 @@
         </is>
       </c>
       <c r="N78" s="5" t="inlineStr"/>
-      <c r="O78" s="6" t="n"/>
-      <c r="P78" s="6" t="n"/>
+      <c r="O78" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P78" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Concrete; A uses jargon-ish "câu ranh giới"</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="34" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
@@ -16635,8 +18315,16 @@
         </is>
       </c>
       <c r="N79" s="5" t="inlineStr"/>
-      <c r="O79" s="6" t="n"/>
-      <c r="P79" s="6" t="n"/>
+      <c r="O79" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P79" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Avoids repeating "chín giờ" chosen in next/criterion</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="34" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
@@ -16705,8 +18393,16 @@
         </is>
       </c>
       <c r="N80" s="5" t="inlineStr"/>
-      <c r="O80" s="6" t="n"/>
-      <c r="P80" s="6" t="n"/>
+      <c r="O80" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P80" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Self-care rule: concrete; A "chịu" heavy</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="34" customHeight="1">
       <c r="A81" s="5" t="inlineStr">
@@ -16775,8 +18471,16 @@
         </is>
       </c>
       <c r="N81" s="5" t="inlineStr"/>
-      <c r="O81" s="6" t="n"/>
-      <c r="P81" s="6" t="n"/>
+      <c r="O81" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P81" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Warm, neutral; A repeats the 9pm example</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="34" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
@@ -16845,8 +18549,16 @@
         </is>
       </c>
       <c r="N82" s="5" t="inlineStr"/>
-      <c r="O82" s="6" t="n"/>
-      <c r="P82" s="6" t="n"/>
+      <c r="O82" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P82" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. B substitutes a different small closing</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="49" customHeight="1">
       <c r="A83" s="5" t="inlineStr">
@@ -16915,8 +18627,16 @@
         </is>
       </c>
       <c r="N83" s="5" t="inlineStr"/>
-      <c r="O83" s="6" t="n"/>
-      <c r="P83" s="6" t="n"/>
+      <c r="O83" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P83" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="34" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
@@ -16985,8 +18705,16 @@
         </is>
       </c>
       <c r="N84" s="5" t="inlineStr"/>
-      <c r="O84" s="6" t="n"/>
-      <c r="P84" s="6" t="n"/>
+      <c r="O84" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P84" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. A relationship-argument only</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="34" customHeight="1">
       <c r="A85" s="5" t="inlineStr">
@@ -17055,8 +18783,16 @@
         </is>
       </c>
       <c r="N85" s="5" t="inlineStr"/>
-      <c r="O85" s="6" t="n"/>
-      <c r="P85" s="6" t="n"/>
+      <c r="O85" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P85" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. B duplicates noi_ra criterion template</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="34" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
@@ -17125,8 +18861,16 @@
         </is>
       </c>
       <c r="N86" s="5" t="inlineStr"/>
-      <c r="O86" s="6" t="n"/>
-      <c r="P86" s="6" t="n"/>
+      <c r="O86" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P86" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. B work-only</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="34" customHeight="1">
       <c r="A87" s="5" t="inlineStr">
@@ -17195,8 +18939,16 @@
         </is>
       </c>
       <c r="N87" s="5" t="inlineStr"/>
-      <c r="O87" s="6" t="n"/>
-      <c r="P87" s="6" t="n"/>
+      <c r="O87" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P87" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="49" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
@@ -17265,8 +19017,16 @@
         </is>
       </c>
       <c r="N88" s="5" t="inlineStr"/>
-      <c r="O88" s="6" t="n"/>
-      <c r="P88" s="6" t="n"/>
+      <c r="O88" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P88" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Verify</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="34" customHeight="1">
       <c r="A89" s="5" t="inlineStr">
@@ -17335,8 +19095,16 @@
         </is>
       </c>
       <c r="N89" s="5" t="inlineStr"/>
-      <c r="O89" s="6" t="n"/>
-      <c r="P89" s="6" t="n"/>
+      <c r="O89" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P89" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Topic-neutral</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="34" customHeight="1">
       <c r="A90" s="5" t="inlineStr">
@@ -17405,8 +19173,16 @@
         </is>
       </c>
       <c r="N90" s="5" t="inlineStr"/>
-      <c r="O90" s="6" t="n"/>
-      <c r="P90" s="6" t="n"/>
+      <c r="O90" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P90" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Fits all topics incl. ex</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="34" customHeight="1">
       <c r="A91" s="5" t="inlineStr">
@@ -17475,8 +19251,16 @@
         </is>
       </c>
       <c r="N91" s="5" t="inlineStr"/>
-      <c r="O91" s="6" t="n"/>
-      <c r="P91" s="6" t="n"/>
+      <c r="O91" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P91" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Fits communication/relationships</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="64" customHeight="1">
       <c r="A92" s="5" t="inlineStr">
@@ -17549,8 +19333,16 @@
           <t>opening — Học thêm là việc một mình; trải 5 lá trò chuyện chỉ được chọn khi câu có chữ nhắn/nói, lúc đó nhãn giao tiếp thắng.</t>
         </is>
       </c>
-      <c r="O92" s="6" t="n"/>
-      <c r="P92" s="6" t="n"/>
+      <c r="O92" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P92" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Does it now</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="49" customHeight="1">
       <c r="A93" s="5" t="inlineStr">
@@ -17619,8 +19411,16 @@
         </is>
       </c>
       <c r="N93" s="5" t="inlineStr"/>
-      <c r="O93" s="6" t="n"/>
-      <c r="P93" s="6" t="n"/>
+      <c r="O93" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P93" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Verify</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="34" customHeight="1">
       <c r="A94" s="5" t="inlineStr">
@@ -17689,8 +19489,16 @@
         </is>
       </c>
       <c r="N94" s="5" t="inlineStr"/>
-      <c r="O94" s="6" t="n"/>
-      <c r="P94" s="6" t="n"/>
+      <c r="O94" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P94" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="34" customHeight="1">
       <c r="A95" s="5" t="inlineStr">
@@ -17759,8 +19567,16 @@
         </is>
       </c>
       <c r="N95" s="5" t="inlineStr"/>
-      <c r="O95" s="6" t="n"/>
-      <c r="P95" s="6" t="n"/>
+      <c r="O95" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P95" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Varies from bat_dau criterion B</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="49" customHeight="1">
       <c r="A96" s="5" t="inlineStr">
@@ -17833,8 +19649,16 @@
           <t>opening — Tập trung là việc một mình; câu có chữ nói chuyện sẽ khớp nhãn nói ra.</t>
         </is>
       </c>
-      <c r="O96" s="6" t="n"/>
-      <c r="P96" s="6" t="n"/>
+      <c r="O96" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P96" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Topic-neutral (reading too)</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="49" customHeight="1">
       <c r="A97" s="5" t="inlineStr">
@@ -17903,8 +19727,16 @@
         </is>
       </c>
       <c r="N97" s="5" t="inlineStr"/>
-      <c r="O97" s="6" t="n"/>
-      <c r="P97" s="6" t="n"/>
+      <c r="O97" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P97" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. A is 15 minutes (&gt;10)</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="34" customHeight="1">
       <c r="A98" s="5" t="inlineStr">
@@ -17973,8 +19805,16 @@
         </is>
       </c>
       <c r="N98" s="5" t="inlineStr"/>
-      <c r="O98" s="6" t="n"/>
-      <c r="P98" s="6" t="n"/>
+      <c r="O98" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P98" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. B duplicates focus B</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="34" customHeight="1">
       <c r="A99" s="5" t="inlineStr">
@@ -18043,8 +19883,16 @@
         </is>
       </c>
       <c r="N99" s="5" t="inlineStr"/>
-      <c r="O99" s="6" t="n"/>
-      <c r="P99" s="6" t="n"/>
+      <c r="O99" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P99" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Clear</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="34" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
@@ -18113,8 +19961,16 @@
         </is>
       </c>
       <c r="N100" s="5" t="inlineStr"/>
-      <c r="O100" s="6" t="n"/>
-      <c r="P100" s="6" t="n"/>
+      <c r="O100" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P100" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="49" customHeight="1">
       <c r="A101" s="5" t="inlineStr">
@@ -18183,8 +20039,16 @@
         </is>
       </c>
       <c r="N101" s="5" t="inlineStr"/>
-      <c r="O101" s="6" t="n"/>
-      <c r="P101" s="6" t="n"/>
+      <c r="O101" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P101" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. A duplicates focus A</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="34" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
@@ -18253,8 +20117,16 @@
         </is>
       </c>
       <c r="N102" s="5" t="inlineStr"/>
-      <c r="O102" s="6" t="n"/>
-      <c r="P102" s="6" t="n"/>
+      <c r="O102" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P102" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. B is 30 minutes and work-only</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="34" customHeight="1">
       <c r="A103" s="5" t="inlineStr">
@@ -18323,8 +20195,16 @@
         </is>
       </c>
       <c r="N103" s="5" t="inlineStr"/>
-      <c r="O103" s="6" t="n"/>
-      <c r="P103" s="6" t="n"/>
+      <c r="O103" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P103" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="34" customHeight="1">
       <c r="A104" s="5" t="inlineStr">
@@ -18393,8 +20273,16 @@
         </is>
       </c>
       <c r="N104" s="5" t="inlineStr"/>
-      <c r="O104" s="6" t="n"/>
-      <c r="P104" s="6" t="n"/>
+      <c r="O104" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P104" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Fits postpone-date; B work-only</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="34" customHeight="1">
       <c r="A105" s="5" t="inlineStr">
@@ -18463,8 +20351,16 @@
         </is>
       </c>
       <c r="N105" s="5" t="inlineStr"/>
-      <c r="O105" s="6" t="n"/>
-      <c r="P105" s="6" t="n"/>
+      <c r="O105" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P105" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Topic-neutral; A moving-help only</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="49" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
@@ -18533,8 +20429,16 @@
         </is>
       </c>
       <c r="N106" s="5" t="inlineStr"/>
-      <c r="O106" s="6" t="n"/>
-      <c r="P106" s="6" t="n"/>
+      <c r="O106" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P106" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Verify; B overlaps focus B</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="34" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
@@ -18603,8 +20507,16 @@
         </is>
       </c>
       <c r="N107" s="5" t="inlineStr"/>
-      <c r="O107" s="6" t="n"/>
-      <c r="P107" s="6" t="n"/>
+      <c r="O107" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P107" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Vivid swap line</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="34" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
@@ -18673,8 +20585,16 @@
         </is>
       </c>
       <c r="N108" s="5" t="inlineStr"/>
-      <c r="O108" s="6" t="n"/>
-      <c r="P108" s="6" t="n"/>
+      <c r="O108" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P108" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Self-care rule: actually asks</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="34" customHeight="1">
       <c r="A109" s="5" t="inlineStr">
@@ -18743,8 +20663,16 @@
         </is>
       </c>
       <c r="N109" s="5" t="inlineStr"/>
-      <c r="O109" s="6" t="n"/>
-      <c r="P109" s="6" t="n"/>
+      <c r="O109" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P109" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Neutral; B dishes only</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="34" customHeight="1">
       <c r="A110" s="5" t="inlineStr">
@@ -18813,8 +20741,16 @@
         </is>
       </c>
       <c r="N110" s="5" t="inlineStr"/>
-      <c r="O110" s="6" t="n"/>
-      <c r="P110" s="6" t="n"/>
+      <c r="O110" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P110" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Warm, balanced</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="49" customHeight="1">
       <c r="A111" s="5" t="inlineStr">
@@ -18883,8 +20819,16 @@
         </is>
       </c>
       <c r="N111" s="5" t="inlineStr"/>
-      <c r="O111" s="6" t="n"/>
-      <c r="P111" s="6" t="n"/>
+      <c r="O111" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P111" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Consent first</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="34" customHeight="1">
       <c r="A112" s="5" t="inlineStr">
@@ -18953,8 +20897,16 @@
         </is>
       </c>
       <c r="N112" s="5" t="inlineStr"/>
-      <c r="O112" s="6" t="n"/>
-      <c r="P112" s="6" t="n"/>
+      <c r="O112" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P112" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Shorter, broader</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="34" customHeight="1">
       <c r="A113" s="5" t="inlineStr">
@@ -19023,8 +20975,16 @@
         </is>
       </c>
       <c r="N113" s="5" t="inlineStr"/>
-      <c r="O113" s="6" t="n"/>
-      <c r="P113" s="6" t="n"/>
+      <c r="O113" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P113" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Broader principle</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="34" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
@@ -19093,8 +21053,16 @@
         </is>
       </c>
       <c r="N114" s="5" t="inlineStr"/>
-      <c r="O114" s="6" t="n"/>
-      <c r="P114" s="6" t="n"/>
+      <c r="O114" s="6" t="inlineStr">
+        <is>
+          <t>Sửa</t>
+        </is>
+      </c>
+      <c r="P114" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: viết lại → Mở lời: “Mình góp một ý nhỏ về chỗ này nhé, bạn thấy hợp thì dùng.” (A work-only (số liệu cũ), B partner-lateness only; step renders for all 4 topics). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="34" customHeight="1">
       <c r="A115" s="5" t="inlineStr">
@@ -19163,8 +21131,16 @@
         </is>
       </c>
       <c r="N115" s="5" t="inlineStr"/>
-      <c r="O115" s="6" t="n"/>
-      <c r="P115" s="6" t="n"/>
+      <c r="O115" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P115" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Topic-neutral</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="49" customHeight="1">
       <c r="A116" s="5" t="inlineStr">
@@ -19233,8 +21209,16 @@
         </is>
       </c>
       <c r="N116" s="5" t="inlineStr"/>
-      <c r="O116" s="6" t="n"/>
-      <c r="P116" s="6" t="n"/>
+      <c r="O116" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P116" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Doable now; A spans a week</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="34" customHeight="1">
       <c r="A117" s="5" t="inlineStr">
@@ -19303,8 +21287,16 @@
         </is>
       </c>
       <c r="N117" s="5" t="inlineStr"/>
-      <c r="O117" s="6" t="n"/>
-      <c r="P117" s="6" t="n"/>
+      <c r="O117" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P117" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Broader</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="34" customHeight="1">
       <c r="A118" s="5" t="inlineStr">
@@ -19373,8 +21365,16 @@
         </is>
       </c>
       <c r="N118" s="5" t="inlineStr"/>
-      <c r="O118" s="6" t="n"/>
-      <c r="P118" s="6" t="n"/>
+      <c r="O118" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P118" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Clear</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="34" customHeight="1">
       <c r="A119" s="5" t="inlineStr">
@@ -19443,8 +21443,16 @@
         </is>
       </c>
       <c r="N119" s="5" t="inlineStr"/>
-      <c r="O119" s="6" t="n"/>
-      <c r="P119" s="6" t="n"/>
+      <c r="O119" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P119" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. B chores only</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="34" customHeight="1">
       <c r="A120" s="5" t="inlineStr">
@@ -19517,8 +21525,16 @@
           <t>opening — Dọn dẹp là việc một mình; không có câu mở lời tự nhiên.</t>
         </is>
       </c>
-      <c r="O120" s="6" t="n"/>
-      <c r="P120" s="6" t="n"/>
+      <c r="O120" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P120" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Timer plus one surface</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="49" customHeight="1">
       <c r="A121" s="5" t="inlineStr">
@@ -19587,8 +21603,16 @@
         </is>
       </c>
       <c r="N121" s="5" t="inlineStr"/>
-      <c r="O121" s="6" t="n"/>
-      <c r="P121" s="6" t="n"/>
+      <c r="O121" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P121" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Verify</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="34" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
@@ -19657,8 +21681,16 @@
         </is>
       </c>
       <c r="N122" s="5" t="inlineStr"/>
-      <c r="O122" s="6" t="n"/>
-      <c r="P122" s="6" t="n"/>
+      <c r="O122" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P122" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="34" customHeight="1">
       <c r="A123" s="5" t="inlineStr">
@@ -19727,8 +21759,16 @@
         </is>
       </c>
       <c r="N123" s="5" t="inlineStr"/>
-      <c r="O123" s="6" t="n"/>
-      <c r="P123" s="6" t="n"/>
+      <c r="O123" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P123" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="49" customHeight="1">
       <c r="A124" s="5" t="inlineStr">
@@ -19801,8 +21841,16 @@
           <t>opening — Ra ngoài một mình không cần mở lời; rủ người khác khớp nhãn hẹn gặp.</t>
         </is>
       </c>
-      <c r="O124" s="6" t="n"/>
-      <c r="P124" s="6" t="n"/>
+      <c r="O124" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P124" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Actually goes out</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="49" customHeight="1">
       <c r="A125" s="5" t="inlineStr">
@@ -19871,8 +21919,16 @@
         </is>
       </c>
       <c r="N125" s="5" t="inlineStr"/>
-      <c r="O125" s="6" t="n"/>
-      <c r="P125" s="6" t="n"/>
+      <c r="O125" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P125" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. A is 15 minutes (&gt;10)</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="34" customHeight="1">
       <c r="A126" s="5" t="inlineStr">
@@ -19941,8 +21997,16 @@
         </is>
       </c>
       <c r="N126" s="5" t="inlineStr"/>
-      <c r="O126" s="6" t="n"/>
-      <c r="P126" s="6" t="n"/>
+      <c r="O126" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P126" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="34" customHeight="1">
       <c r="A127" s="5" t="inlineStr">
@@ -20011,8 +22075,16 @@
         </is>
       </c>
       <c r="N127" s="5" t="inlineStr"/>
-      <c r="O127" s="6" t="n"/>
-      <c r="P127" s="6" t="n"/>
+      <c r="O127" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P127" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Clear</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="49" customHeight="1">
       <c r="A128" s="5" t="inlineStr">
@@ -20085,8 +22157,16 @@
           <t>opening — Báo vắng đã có ở bước tập trung; câu có chữ nhắn/nói sẽ khớp nhãn giao tiếp.</t>
         </is>
       </c>
-      <c r="O128" s="6" t="n"/>
-      <c r="P128" s="6" t="n"/>
+      <c r="O128" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P128" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. A "ở nhà nghỉ" reads as "at a motel"</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="49" customHeight="1">
       <c r="A129" s="5" t="inlineStr">
@@ -20155,8 +22235,16 @@
         </is>
       </c>
       <c r="N129" s="5" t="inlineStr"/>
-      <c r="O129" s="6" t="n"/>
-      <c r="P129" s="6" t="n"/>
+      <c r="O129" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P129" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Bản A kéo dài cả buổi tối; B chọn một việc cụ thể</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="34" customHeight="1">
       <c r="A130" s="5" t="inlineStr">
@@ -20225,8 +22313,16 @@
         </is>
       </c>
       <c r="N130" s="5" t="inlineStr"/>
-      <c r="O130" s="6" t="n"/>
-      <c r="P130" s="6" t="n"/>
+      <c r="O130" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P130" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="34" customHeight="1">
       <c r="A131" s="5" t="inlineStr">
@@ -20295,8 +22391,16 @@
         </is>
       </c>
       <c r="N131" s="5" t="inlineStr"/>
-      <c r="O131" s="6" t="n"/>
-      <c r="P131" s="6" t="n"/>
+      <c r="O131" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P131" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Clear</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="34" customHeight="1">
       <c r="A132" s="5" t="inlineStr">
@@ -20369,8 +22473,16 @@
           <t>opening — Đổi thói quen là việc một mình; không có câu mở lời tự nhiên.</t>
         </is>
       </c>
-      <c r="O132" s="6" t="n"/>
-      <c r="P132" s="6" t="n"/>
+      <c r="O132" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P132" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Concrete</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="49" customHeight="1">
       <c r="A133" s="5" t="inlineStr">
@@ -20439,8 +22551,16 @@
         </is>
       </c>
       <c r="N133" s="5" t="inlineStr"/>
-      <c r="O133" s="6" t="n"/>
-      <c r="P133" s="6" t="n"/>
+      <c r="O133" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P133" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Observe first; A repeats focus B</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="34" customHeight="1">
       <c r="A134" s="5" t="inlineStr">
@@ -20509,8 +22629,16 @@
         </is>
       </c>
       <c r="N134" s="5" t="inlineStr"/>
-      <c r="O134" s="6" t="n"/>
-      <c r="P134" s="6" t="n"/>
+      <c r="O134" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P134" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Topic-neutral (fits coffee too)</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="49" customHeight="1">
       <c r="A135" s="5" t="inlineStr">
@@ -20579,8 +22707,16 @@
         </is>
       </c>
       <c r="N135" s="5" t="inlineStr"/>
-      <c r="O135" s="6" t="n"/>
-      <c r="P135" s="6" t="n"/>
+      <c r="O135" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P135" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Shorter; A 27 words</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="34" customHeight="1">
       <c r="A136" s="5" t="inlineStr">
@@ -20653,8 +22789,16 @@
           <t>opening — Tự thưởng là việc một mình; không có câu mở lời tự nhiên.</t>
         </is>
       </c>
-      <c r="O136" s="6" t="n"/>
-      <c r="P136" s="6" t="n"/>
+      <c r="O136" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P136" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Does it</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="49" customHeight="1">
       <c r="A137" s="5" t="inlineStr">
@@ -20723,8 +22867,16 @@
         </is>
       </c>
       <c r="N137" s="5" t="inlineStr"/>
-      <c r="O137" s="6" t="n"/>
-      <c r="P137" s="6" t="n"/>
+      <c r="O137" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P137" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Distinct; A overlaps focus</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="34" customHeight="1">
       <c r="A138" s="5" t="inlineStr">
@@ -20793,8 +22945,16 @@
         </is>
       </c>
       <c r="N138" s="5" t="inlineStr"/>
-      <c r="O138" s="6" t="n"/>
-      <c r="P138" s="6" t="n"/>
+      <c r="O138" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P138" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. B overlaps next B</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="34" customHeight="1">
       <c r="A139" s="5" t="inlineStr">
@@ -20863,8 +23023,16 @@
         </is>
       </c>
       <c r="N139" s="5" t="inlineStr"/>
-      <c r="O139" s="6" t="n"/>
-      <c r="P139" s="6" t="n"/>
+      <c r="O139" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P139" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Self-care rule: reward now; A defers</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="49" customHeight="1">
       <c r="A140" s="5" t="inlineStr">
@@ -20937,8 +23105,16 @@
           <t>opening — Viết ra là việc một mình; câu có chữ nói chuyện sẽ khớp nhãn nói ra.</t>
         </is>
       </c>
-      <c r="O140" s="6" t="n"/>
-      <c r="P140" s="6" t="n"/>
+      <c r="O140" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P140" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="49" customHeight="1">
       <c r="A141" s="5" t="inlineStr">
@@ -21007,8 +23183,16 @@
         </is>
       </c>
       <c r="N141" s="5" t="inlineStr"/>
-      <c r="O141" s="6" t="n"/>
-      <c r="P141" s="6" t="n"/>
+      <c r="O141" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P141" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản B. Fits most topics; A only "điều muốn nói"</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="34" customHeight="1">
       <c r="A142" s="5" t="inlineStr">
@@ -21077,8 +23261,16 @@
         </is>
       </c>
       <c r="N142" s="5" t="inlineStr"/>
-      <c r="O142" s="6" t="n"/>
-      <c r="P142" s="6" t="n"/>
+      <c r="O142" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P142" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. B "định nhớ trong đầu" unnatural</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="34" customHeight="1">
       <c r="A143" s="5" t="inlineStr">
@@ -21147,8 +23339,16 @@
         </is>
       </c>
       <c r="N143" s="5" t="inlineStr"/>
-      <c r="O143" s="6" t="n"/>
-      <c r="P143" s="6" t="n"/>
+      <c r="O143" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="P143" s="6" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: chọn bản A. Concrete</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:P143"/>

--- a/docs/reviews/2026-10-22-t02-t03-tarot-copy-workbook.xlsx
+++ b/docs/reviews/2026-10-22-t02-t03-tarot-copy-workbook.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="49" customHeight="1">
+    <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Trạng thái</t>
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>BẢN NHÁP chờ chủ sản phẩm duyệt. Chưa câu nào trong file này chạy trên app. Không có gì được nối vào engine hay vùng duyệt fallback cho tới khi owner duyệt; việc nối làm ở một PR riêng sau đó, giữ nguyên các bài đã rút (đóng băng theo phiên, US-20 AC15/AC17).</t>
+          <t xml:space="preserve">Đã có quyết định theo uỷ quyền ngày 26/10/2026; Codex chuốt câu chữ, Claude review bản sửa. Chưa nối vào app hay kho fallback. Việc nối làm ở PR riêng và giữ nguyên các bài đã rút.</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6411,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="34" customHeight="1">
+    <row r="68" ht="48" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
           <t>T02-chia_se-self_care</t>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="R68" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Cả tuần bạn trả lời mọi lời hỏi thăm bằng “mình ổn”, trong khi chuyện làm bạn bận lòng vẫn chưa kể với ai. (A ends in a dark room alone (heavy for a calm app); B is writing, not sharing). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Cả tuần bạn trả lời “mình ổn” mỗi khi được hỏi thăm, rồi chuyển sang chuyện khác. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -12554,7 +12554,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="48" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>T03-nhan_loi-opening</t>
@@ -12628,7 +12628,7 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Mở lời: “Mình nhận nhé, mình chốt lại giờ giấc cụ thể với bạn được không?” (Both drafts are work-only (weekdays / hạn chót) but step renders for movie date, moving help, dinner). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Mở lời: “Mình nhận lời nhé, mình thống nhất thời gian cụ thể với bạn được không?” | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -17624,7 +17624,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="34" customHeight="1">
+    <row r="71" ht="48" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
           <t>T03-hen_gap-opening</t>
@@ -17698,7 +17698,7 @@
       </c>
       <c r="P71" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Mở lời: “Cuối tuần này bạn rảnh không, mình đi cà phê một chút nhé?” (A "Lâu rồi không gặp" wrong for new acquaintance row; B texting-only). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Mở lời: “Bạn rảnh lúc nào để mình hẹn gặp và nói chuyện một chút?” | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -20986,7 +20986,7 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="34" customHeight="1">
+    <row r="114" ht="48" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
         <is>
           <t>T03-gop_y-opening</t>
@@ -21060,7 +21060,7 @@
       </c>
       <c r="P114" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Mở lời: “Mình góp một ý nhỏ về chỗ này nhé, bạn thấy hợp thì dùng.” (A work-only (số liệu cũ), B partner-lateness only; step renders for all 4 topics). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Mở lời: “Bạn có muốn nghe một góp ý của mình về chuyện này không?” | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
